--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B3" t="n">
-        <v>97526</v>
+        <v>56840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R3" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>56840</v>
+        <v>97526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R4" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>97526</v>
+        <v>97527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,48 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127314113</v>
+        <v>127313434</v>
       </c>
       <c r="B5" t="n">
-        <v>90825</v>
+        <v>82855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5745</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ansättån, Ansättån, Jmt</t>
+          <t>Flatrun, Flatrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446624</v>
+        <v>446268</v>
       </c>
       <c r="R5" t="n">
-        <v>7087286</v>
+        <v>7086926</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,18 +1054,12 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Preliminärt, måste utredas mer.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,108 +1080,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>127313434</v>
-      </c>
-      <c r="B6" t="n">
-        <v>82855</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Flatrun, Flatrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>446268</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7086926</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bördig och örtrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B3" t="n">
-        <v>56840</v>
+        <v>97527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R3" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B4" t="n">
-        <v>97527</v>
+        <v>56840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R4" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B3" t="n">
-        <v>97527</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R3" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>56840</v>
+        <v>97531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R4" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127313434</v>
       </c>
       <c r="B5" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>97531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R3" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B4" t="n">
-        <v>97531</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R4" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B3" t="n">
-        <v>97531</v>
+        <v>56846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R3" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R4" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127313434</v>
       </c>
       <c r="B5" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127313663</v>
       </c>
       <c r="B3" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>97539</v>
+        <v>97542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127313434</v>
       </c>
       <c r="B5" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>97550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R3" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B4" t="n">
-        <v>97542</v>
+        <v>56855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R4" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127313434</v>
       </c>
       <c r="B5" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B3" t="n">
-        <v>97550</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R3" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B4" t="n">
-        <v>56855</v>
+        <v>97551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R4" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63787-2020 artfynd.xlsx
+++ b/artfynd/A 63787-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127312260</v>
       </c>
       <c r="B2" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127313663</v>
+        <v>127313857</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>97552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446376</v>
+        <v>446482</v>
       </c>
       <c r="R3" t="n">
-        <v>7087028</v>
+        <v>7087175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127313857</v>
+        <v>127313663</v>
       </c>
       <c r="B4" t="n">
-        <v>97551</v>
+        <v>56855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446482</v>
+        <v>446376</v>
       </c>
       <c r="R4" t="n">
-        <v>7087175</v>
+        <v>7087028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
